--- a/GBDS APRIL FILES 2026/SCRR CALCULATOR - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/SCRR CALCULATOR - APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A0640F-BE13-4890-A296-08F63FC87D09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C669F94D-0B16-4E01-B39C-BADFE0496AAC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="18" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="27" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(APRIL 2026)" sheetId="814" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5404" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5410" uniqueCount="160">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -666,6 +666,18 @@
   </si>
   <si>
     <t>52598</t>
+  </si>
+  <si>
+    <t>FB BOTT.</t>
+  </si>
+  <si>
+    <t>2120007646</t>
+  </si>
+  <si>
+    <t>2122212974</t>
+  </si>
+  <si>
+    <t>2000008074</t>
   </si>
 </sst>
 </file>
@@ -44370,10 +44382,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>535</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>407135</v>
       </c>
       <c r="F6" s="123" t="s">
         <v>16</v>
@@ -44406,10 +44420,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>2</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1562</v>
       </c>
       <c r="F7" s="124"/>
       <c r="G7" s="128"/>
@@ -44458,10 +44474,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>20</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14660</v>
       </c>
       <c r="F9" s="124"/>
       <c r="G9" s="136"/>
@@ -44542,10 +44560,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="F12" s="142" t="s">
         <v>33</v>
@@ -44576,10 +44596,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>6</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1842</v>
       </c>
       <c r="F13" s="145" t="s">
         <v>36</v>
@@ -44587,7 +44609,7 @@
       <c r="G13" s="146"/>
       <c r="H13" s="147">
         <f>D29</f>
-        <v>0</v>
+        <v>426678</v>
       </c>
       <c r="I13" s="148"/>
       <c r="J13" s="149"/>
@@ -44610,10 +44632,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>3</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F14" s="150" t="s">
         <v>38</v>
@@ -44621,7 +44645,7 @@
       <c r="G14" s="151"/>
       <c r="H14" s="152">
         <f>D54</f>
-        <v>0</v>
+        <v>60252</v>
       </c>
       <c r="I14" s="153"/>
       <c r="J14" s="154"/>
@@ -44659,7 +44683,7 @@
       <c r="G15" s="146"/>
       <c r="H15" s="156">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>366426</v>
       </c>
       <c r="I15" s="157"/>
       <c r="J15" s="158"/>
@@ -44951,12 +44975,14 @@
     <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="121"/>
       <c r="B24" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="10"/>
+        <v>156</v>
+      </c>
+      <c r="C24" s="10">
+        <v>12</v>
+      </c>
       <c r="D24" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="F24" s="77"/>
       <c r="G24" s="79"/>
@@ -45122,7 +45148,7 @@
       <c r="C29" s="162"/>
       <c r="D29" s="166">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>426678</v>
       </c>
       <c r="F29" s="168" t="s">
         <v>54</v>
@@ -45130,7 +45156,7 @@
       <c r="G29" s="169"/>
       <c r="H29" s="172">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27+H28</f>
-        <v>0</v>
+        <v>366426</v>
       </c>
       <c r="I29" s="173"/>
       <c r="J29" s="174"/>
@@ -45269,10 +45295,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="40">
+        <v>94</v>
+      </c>
       <c r="H34" s="200">
         <f t="shared" ref="H34:H39" si="2">F34*G34</f>
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="I34" s="201"/>
       <c r="J34" s="202"/>
@@ -45303,10 +45331,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>41</v>
+      </c>
       <c r="H35" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="I35" s="201"/>
       <c r="J35" s="202"/>
@@ -45327,18 +45357,22 @@
       <c r="B36" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10">
+        <v>1</v>
+      </c>
       <c r="D36" s="12">
         <f>C36*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F36" s="12">
         <v>200</v>
       </c>
-      <c r="G36" s="37"/>
+      <c r="G36" s="37">
+        <v>1</v>
+      </c>
       <c r="H36" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I36" s="201"/>
       <c r="J36" s="202"/>
@@ -45363,18 +45397,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>509</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>56499</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>49</v>
+      </c>
       <c r="H37" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="I37" s="201"/>
       <c r="J37" s="202"/>
@@ -45397,18 +45435,22 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>22</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>1848</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>76</v>
+      </c>
       <c r="H38" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="I38" s="201"/>
       <c r="J38" s="202"/>
@@ -45431,18 +45473,22 @@
       <c r="B39" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>2</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="37">
+        <v>2</v>
+      </c>
       <c r="H39" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I39" s="201"/>
       <c r="J39" s="202"/>
@@ -45465,10 +45511,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>4</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -45496,10 +45544,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>1</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -45528,15 +45578,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>4</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="200"/>
+      <c r="G42" s="200">
+        <v>23</v>
+      </c>
       <c r="H42" s="201"/>
       <c r="I42" s="201"/>
       <c r="J42" s="202"/>
@@ -45587,14 +45641,22 @@
       <c r="B44" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>3</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="184"/>
+        <v>360</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="G44" s="99" t="s">
+        <v>157</v>
+      </c>
+      <c r="H44" s="184">
+        <v>140000</v>
+      </c>
       <c r="I44" s="184"/>
       <c r="J44" s="184"/>
       <c r="K44" s="21"/>
@@ -45617,14 +45679,22 @@
       <c r="B45" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>1</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="37"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="184"/>
+        <v>84</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" s="99" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="184">
+        <v>104214</v>
+      </c>
       <c r="I45" s="184"/>
       <c r="J45" s="184"/>
       <c r="K45" s="21"/>
@@ -45637,10 +45707,12 @@
       <c r="B46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="81"/>
+      <c r="C46" s="81">
+        <v>8</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="62"/>
@@ -45674,10 +45746,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>11</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -45712,7 +45786,7 @@
       </c>
       <c r="G49" s="172">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>367677</v>
       </c>
       <c r="H49" s="173"/>
       <c r="I49" s="173"/>
@@ -45736,10 +45810,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>29</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="F50" s="226"/>
       <c r="G50" s="175"/>
@@ -45761,15 +45837,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="227" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" s="239">
+        <v>115</v>
+      </c>
+      <c r="G51" s="229">
         <f>G49-H29</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="240"/>
-      <c r="I51" s="240"/>
-      <c r="J51" s="241"/>
+        <v>1251</v>
+      </c>
+      <c r="H51" s="230"/>
+      <c r="I51" s="230"/>
+      <c r="J51" s="231"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>86</v>
@@ -45791,10 +45867,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="228"/>
-      <c r="G52" s="242"/>
-      <c r="H52" s="243"/>
-      <c r="I52" s="243"/>
-      <c r="J52" s="244"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="233"/>
+      <c r="I52" s="233"/>
+      <c r="J52" s="234"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>87</v>
@@ -45836,7 +45912,7 @@
       <c r="C54" s="214"/>
       <c r="D54" s="217">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>60252</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -46101,10 +46177,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>317</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>241237</v>
       </c>
       <c r="F6" s="123" t="s">
         <v>16</v>
@@ -46137,10 +46215,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>3</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="F7" s="124"/>
       <c r="G7" s="128"/>
@@ -46189,10 +46269,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>12</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8796</v>
       </c>
       <c r="F9" s="124"/>
       <c r="G9" s="136"/>
@@ -46273,10 +46355,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="F12" s="142" t="s">
         <v>33</v>
@@ -46307,10 +46391,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>11</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="F13" s="145" t="s">
         <v>36</v>
@@ -46318,7 +46404,7 @@
       <c r="G13" s="146"/>
       <c r="H13" s="147">
         <f>D29</f>
-        <v>0</v>
+        <v>256965</v>
       </c>
       <c r="I13" s="148"/>
       <c r="J13" s="149"/>
@@ -46341,10 +46427,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>20</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="F14" s="150" t="s">
         <v>38</v>
@@ -46352,7 +46440,7 @@
       <c r="G14" s="151"/>
       <c r="H14" s="152">
         <f>D54</f>
-        <v>0</v>
+        <v>37854</v>
       </c>
       <c r="I14" s="153"/>
       <c r="J14" s="154"/>
@@ -46390,7 +46478,7 @@
       <c r="G15" s="146"/>
       <c r="H15" s="156">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>219111</v>
       </c>
       <c r="I15" s="157"/>
       <c r="J15" s="158"/>
@@ -46429,7 +46517,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="159"/>
+      <c r="H16" s="159">
+        <v>1296</v>
+      </c>
       <c r="I16" s="159"/>
       <c r="J16" s="159"/>
       <c r="L16" s="6">
@@ -46853,7 +46943,7 @@
       <c r="C29" s="162"/>
       <c r="D29" s="166">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>256965</v>
       </c>
       <c r="F29" s="168" t="s">
         <v>54</v>
@@ -46861,7 +46951,7 @@
       <c r="G29" s="169"/>
       <c r="H29" s="172">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>217815</v>
       </c>
       <c r="I29" s="173"/>
       <c r="J29" s="174"/>
@@ -47000,10 +47090,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="74"/>
+      <c r="G34" s="74">
+        <v>59</v>
+      </c>
       <c r="H34" s="200">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="I34" s="201"/>
       <c r="J34" s="202"/>
@@ -47034,10 +47126,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>253</v>
+      </c>
       <c r="H35" s="200">
         <f t="shared" ref="H35:H39" si="2">F35*G35</f>
-        <v>0</v>
+        <v>126500</v>
       </c>
       <c r="I35" s="201"/>
       <c r="J35" s="202"/>
@@ -47094,18 +47188,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>330</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>36630</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>217</v>
+      </c>
       <c r="H37" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="I37" s="201"/>
       <c r="J37" s="202"/>
@@ -47128,18 +47226,22 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>1</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>205</v>
+      </c>
       <c r="H38" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10250</v>
       </c>
       <c r="I38" s="201"/>
       <c r="J38" s="202"/>
@@ -47170,10 +47272,12 @@
       <c r="F39" s="12">
         <v>20</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="37">
+        <v>3</v>
+      </c>
       <c r="H39" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I39" s="201"/>
       <c r="J39" s="202"/>
@@ -47196,10 +47300,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>2</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -47227,10 +47333,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>1</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -47259,15 +47367,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>8</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="200"/>
+      <c r="G42" s="200">
+        <v>118</v>
+      </c>
       <c r="H42" s="201"/>
       <c r="I42" s="201"/>
       <c r="J42" s="202"/>
@@ -47348,10 +47460,12 @@
       <c r="B45" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>1</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="62"/>
@@ -47368,10 +47482,12 @@
       <c r="B46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="81"/>
+      <c r="C46" s="81">
+        <v>5</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="104"/>
@@ -47405,10 +47521,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>4</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -47433,17 +47551,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>9</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="F49" s="225" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="172">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>217628</v>
       </c>
       <c r="H49" s="173"/>
       <c r="I49" s="173"/>
@@ -47467,10 +47587,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>23</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="F50" s="226"/>
       <c r="G50" s="175"/>
@@ -47492,15 +47614,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="227" t="s">
-        <v>112</v>
-      </c>
-      <c r="G51" s="229">
+        <v>143</v>
+      </c>
+      <c r="G51" s="239">
         <f>G49-H29</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="230"/>
-      <c r="I51" s="230"/>
-      <c r="J51" s="231"/>
+        <v>-187</v>
+      </c>
+      <c r="H51" s="240"/>
+      <c r="I51" s="240"/>
+      <c r="J51" s="241"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>86</v>
@@ -47522,10 +47644,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="228"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="233"/>
-      <c r="I52" s="233"/>
-      <c r="J52" s="234"/>
+      <c r="G52" s="242"/>
+      <c r="H52" s="243"/>
+      <c r="I52" s="243"/>
+      <c r="J52" s="244"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>87</v>
@@ -47567,7 +47689,7 @@
       <c r="C54" s="214"/>
       <c r="D54" s="217">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>37854</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -47832,10 +47954,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>523</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>398003</v>
       </c>
       <c r="F6" s="123" t="s">
         <v>16</v>
@@ -47868,10 +47992,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>32</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24992</v>
       </c>
       <c r="F7" s="124"/>
       <c r="G7" s="128"/>
@@ -47920,10 +48046,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>19</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13927</v>
       </c>
       <c r="F9" s="124"/>
       <c r="G9" s="136"/>
@@ -47972,10 +48100,12 @@
       <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="10">
+        <v>1</v>
+      </c>
       <c r="D11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="F11" s="124"/>
       <c r="G11" s="136"/>
@@ -48004,10 +48134,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>3</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2976</v>
       </c>
       <c r="F12" s="142" t="s">
         <v>33</v>
@@ -48038,10 +48170,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>18</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5526</v>
       </c>
       <c r="F13" s="145" t="s">
         <v>36</v>
@@ -48049,7 +48183,7 @@
       <c r="G13" s="146"/>
       <c r="H13" s="147">
         <f>D29</f>
-        <v>0</v>
+        <v>448958</v>
       </c>
       <c r="I13" s="148"/>
       <c r="J13" s="149"/>
@@ -48072,10 +48206,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>2</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F14" s="150" t="s">
         <v>38</v>
@@ -48083,7 +48219,7 @@
       <c r="G14" s="151"/>
       <c r="H14" s="152">
         <f>D54</f>
-        <v>0</v>
+        <v>81078.75</v>
       </c>
       <c r="I14" s="153"/>
       <c r="J14" s="154"/>
@@ -48110,10 +48246,13 @@
       <c r="B15" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="10">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
       <c r="D15" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="F15" s="155" t="s">
         <v>39</v>
@@ -48121,7 +48260,7 @@
       <c r="G15" s="146"/>
       <c r="H15" s="156">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>367879.25</v>
       </c>
       <c r="I15" s="157"/>
       <c r="J15" s="158"/>
@@ -48160,7 +48299,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="159"/>
+      <c r="H16" s="159">
+        <v>1296</v>
+      </c>
       <c r="I16" s="159"/>
       <c r="J16" s="159"/>
       <c r="L16" s="6">
@@ -48221,10 +48362,12 @@
       <c r="B18" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
       <c r="D18" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="F18" s="56"/>
       <c r="G18" s="66" t="s">
@@ -48584,7 +48727,7 @@
       <c r="C29" s="162"/>
       <c r="D29" s="166">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>448958</v>
       </c>
       <c r="F29" s="168" t="s">
         <v>54</v>
@@ -48592,7 +48735,7 @@
       <c r="G29" s="169"/>
       <c r="H29" s="172">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>366583.25</v>
       </c>
       <c r="I29" s="173"/>
       <c r="J29" s="174"/>
@@ -48723,18 +48866,22 @@
       <c r="B34" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="51">
+        <v>6</v>
+      </c>
       <c r="D34" s="30">
         <f>C34*120</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="74"/>
+      <c r="G34" s="74">
+        <v>261</v>
+      </c>
       <c r="H34" s="200">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="I34" s="201"/>
       <c r="J34" s="202"/>
@@ -48765,10 +48912,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>61</v>
+      </c>
       <c r="H35" s="200">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="I35" s="201"/>
       <c r="J35" s="202"/>
@@ -48825,18 +48974,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>650</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>72150</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>145</v>
+      </c>
       <c r="H37" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="I37" s="201"/>
       <c r="J37" s="202"/>
@@ -48859,18 +49012,22 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>18</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>51</v>
+      </c>
       <c r="H38" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="I38" s="201"/>
       <c r="J38" s="202"/>
@@ -48893,18 +49050,22 @@
       <c r="B39" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>5</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="37">
+        <v>3</v>
+      </c>
       <c r="H39" s="200">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I39" s="201"/>
       <c r="J39" s="202"/>
@@ -48927,10 +49088,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>41</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>4551</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -48958,10 +49121,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>3</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -48990,15 +49155,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>11</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>24.75</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="200"/>
+      <c r="G42" s="200">
+        <v>23</v>
+      </c>
       <c r="H42" s="201"/>
       <c r="I42" s="201"/>
       <c r="J42" s="202"/>
@@ -49049,14 +49218,22 @@
       <c r="B44" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>3</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="184"/>
+        <v>360</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="184">
+        <v>59614</v>
+      </c>
       <c r="I44" s="184"/>
       <c r="J44" s="184"/>
       <c r="K44" s="21"/>
@@ -49079,10 +49256,12 @@
       <c r="B45" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>3</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="76"/>
@@ -49099,10 +49278,12 @@
       <c r="B46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="81"/>
+      <c r="C46" s="81">
+        <v>1</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="62"/>
@@ -49136,10 +49317,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>14</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -49164,17 +49347,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>3</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="F49" s="225" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="172">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>368247</v>
       </c>
       <c r="H49" s="173"/>
       <c r="I49" s="173"/>
@@ -49198,10 +49383,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>10</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F50" s="226"/>
       <c r="G50" s="175"/>
@@ -49227,7 +49414,7 @@
       </c>
       <c r="G51" s="229">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>1663.75</v>
       </c>
       <c r="H51" s="230"/>
       <c r="I51" s="230"/>
@@ -49298,7 +49485,7 @@
       <c r="C54" s="214"/>
       <c r="D54" s="217">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>81078.75</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
